--- a/processed_ruby_restored_xlsx/sc203_共有３：皆で遊園地ルート分岐前.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc203_共有３：皆で遊園地ルート分岐前.ss.xlsx
@@ -621,8 +621,8 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>She's probably worried you'll get carried away and end
-up lost.</t>
+          <t>She's probably worried you'll get carried away and
+end up lost.</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -637,9 +637,9 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>We came over on the usual ferry with the bus, but they
-were already worked up on the bus, so it couldn’t be
-helped.</t>
+          <t>We came over on the usual ferry with the bus, but
+they were already worked up on the bus, so it
+couldn’t be helped.</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -915,8 +915,8 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan walks along behind everyone with a prim
-look on her face.</t>
+          <t>Rurichiyo-chan walks along behind everyone with a
+prim look on her face.</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1524,8 +1524,9 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>「Nono-chan's never been to this amusement park before,
-so I don't think she really knows what's what...」</t>
+          <t>「Nono-chan's never been to this amusement park
+before, so I don't think she really knows what's
+what...」</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1832,8 +1833,8 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>After a discussion tangled with everyone’s intentions,
-the rules were finally decided.</t>
+          <t>After a discussion tangled with everyone’s
+intentions, the rules were finally decided.</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1990,8 +1991,8 @@
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>We came all this way looking forward to it, so there's
-no point sulking over small disappointments.</t>
+          <t>We came all this way looking forward to it, so
+there's no point sulking over small disappointments.</t>
         </is>
       </c>
       <c r="C100" t="n">

--- a/processed_ruby_restored_xlsx/sc203_共有３：皆で遊園地ルート分岐前.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc203_共有３：皆で遊園地ルート分岐前.ss.xlsx
@@ -977,7 +977,7 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1371,9 +1371,9 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>「As the chaperone sensei, I suggest you stick with
+          <t>As the chaperone sensei, I suggest you stick with
 either me or Janitor-sensei and don't go off on your
-own！」</t>
+own！</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1924,9 +1924,9 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>「Mui-san, either stay with Janitor-sensei, or
+          <t>Mui-san, either stay with Janitor-sensei, or
 otherwise move around in groups of three or more...
-That's all！」</t>
+That's all！</t>
         </is>
       </c>
       <c r="C96" t="n">
